--- a/Hoadon/HDVao/8/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/8/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TWC</t>
+          <t>C25TBV</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>15/08/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0109690873</t>
+          <t>0304998358-056</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN GIA DỤNG WINCI VIỆT NAM</t>
+          <t>CHI NHÁNH 34 - CÔNG TY CỔ PHẦN THƯƠNG MẠI - DỊCH VỤ PHONG VŨ</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Số 138 Ngõ 13 Đường Khuất Duy Tiến, Phường Thanh Xuân, TP Hà Nội, Việt Nam.</t>
+          <t>L11 G2 Đường Nguyễn Thái Học,phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1.0148148E7</v>
+        <v>360000.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>811852.0</v>
+        <v>0.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>1.096E7</v>
+        <v>360000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +408,54 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TSP</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>346</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>27/08/2025</t>
+          <t>02/08/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0304667885</t>
+          <t>1100119201</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CÔNG TY TNHH HIỆP PHÁT</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>1195 Quốc lộ 1, Khu phố Nhơn Cầu, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>3966667.0</v>
+        <v>7.61E7</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>317333.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>3805000.0</v>
+      </c>
+      <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>4284000.0</v>
+        <v>7.9905E7</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -491,56 +489,54 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25THT</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>453</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>21/08/2025</t>
+          <t>29/08/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3500805921</t>
+          <t>1100119201</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
+          <t>CÔNG TY TNHH HIỆP PHÁT</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 8/18 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>1195 Quốc lộ 1, Khu phố Nhơn Cầu, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1358661.0</v>
+        <v>8.916E7</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>108693.0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>4458000.0</v>
+      </c>
+      <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>1467354.0</v>
+        <v>9.3618E7</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -574,54 +570,56 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TKT</t>
+          <t>C25TTH</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3502219376</t>
+          <t>1100853003</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM TƯƠI SỐNG KIM THU</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGỌC MAI</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 18 Đường Trần Phú, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 46, Nguyễn Văn Cương, Khu phố Nhơn Cầu, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H&amp;V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1.8095E7</v>
+        <v>8.169E7</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>904750.0</v>
-      </c>
-      <c r="M10" s="13"/>
+        <v>4084500.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>1.899975E7</v>
+        <v>8.57745E7</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -655,56 +653,56 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TTH</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>14/08/2025</t>
+          <t>25/08/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>1100853003</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGỌC MAI</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 46, Nguyễn Văn Cương, Khu phố Nhơn Cầu, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>487038.0</v>
+        <v>8.138E7</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>38963.0</v>
+        <v>4069000.0</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>526001.0</v>
+        <v>8.5449E7</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -738,56 +736,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TKN</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>1102099705</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ GẠO KIM NGÂN</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>873 Quốc Lộ 1, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>465740.0</v>
+        <v>8.09E7</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>37259.0</v>
+        <v>4045000.0</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>502999.0</v>
+        <v>8.4945E7</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -821,56 +819,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TNT</t>
+          <t>C25TKN</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>12/08/2025</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502477698</t>
+          <t>1102099705</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MINH TRÍ NGỌC THẢO</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ GẠO KIM NGÂN</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 713 Trương Công Định, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>873 Quốc Lộ 1, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1067172.0</v>
+        <v>8.954E7</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>85374.0</v>
+        <v>4477000.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>52428.0</v>
+        <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>1152546.0</v>
+        <v>9.4017E7</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -904,56 +902,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25TGP</t>
+          <t>C25TKN</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
+          <t>23/08/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3502491396</t>
+          <t>1102099705</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THỰC PHẨM DŨNG PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ GẠO KIM NGÂN</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>353/10, Bùi Thiện Ngộ, phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>873 Quốc Lộ 1, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>1333333.0</v>
+        <v>6.068E7</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>66667.0</v>
+        <v>3034000.0</v>
       </c>
       <c r="M14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>1400000.0</v>
+        <v>6.3714E7</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -987,56 +985,56 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25TGP</t>
+          <t>C25TYA</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>14268</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>27/08/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3502491396</t>
+          <t>1800348038</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THỰC PHẨM DŨNG PHÁT</t>
+          <t>CÔNG TY TNHH ADC</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>353/10, Bùi Thiện Ngộ, phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>101 Phan Đình Phùng, Phường Ninh Kiều, Thành phố Cần Thơ, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>1380952.0</v>
+        <v>6.55E7</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>69048.0</v>
+        <v>3275000.0</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>1450000.0</v>
+        <v>6.8775E7</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1054,668 +1052,6 @@
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>C25TGP</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>13/08/2025</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>3502491396</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THỰC PHẨM DŨNG PHÁT</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>353/10, Bùi Thiện Ngộ, phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="n">
-        <v>1333333.0</v>
-      </c>
-      <c r="L16" s="13" t="n">
-        <v>66667.0</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13" t="n">
-        <v>1400000.0</v>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>C25TGP</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>18/08/2025</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>3502491396</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THỰC PHẨM DŨNG PHÁT</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>353/10, Bùi Thiện Ngộ, phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>1185714.0</v>
-      </c>
-      <c r="L17" s="13" t="n">
-        <v>59286.0</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13" t="n">
-        <v>1245000.0</v>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>C25TGP</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>22/08/2025</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>3502491396</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THỰC PHẨM DŨNG PHÁT</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>353/10, Bùi Thiện Ngộ, phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>1700000.0</v>
-      </c>
-      <c r="L18" s="13" t="n">
-        <v>85000.0</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13" t="n">
-        <v>1785000.0</v>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>C25TGP</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>25/08/2025</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>3502491396</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THỰC PHẨM DŨNG PHÁT</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>353/10, Bùi Thiện Ngộ, phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K19" s="13" t="n">
-        <v>761905.0</v>
-      </c>
-      <c r="L19" s="13" t="n">
-        <v>38095.0</v>
-      </c>
-      <c r="M19" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13" t="n">
-        <v>800000.0</v>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>C25TGP</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>30/08/2025</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>3502491396</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THỰC PHẨM DŨNG PHÁT</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>353/10, Bùi Thiện Ngộ, phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K20" s="13" t="n">
-        <v>5682857.0</v>
-      </c>
-      <c r="L20" s="13" t="n">
-        <v>284143.0</v>
-      </c>
-      <c r="M20" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13" t="n">
-        <v>5967000.0</v>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>C25TNK</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>15/08/2025</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>3502507857</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH XUẤT NHẬP KHẨU BIỂN VIỆT</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>số 89 B Nguyễn Văn Trỗi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty Cổ Phần Đầu Tư Xây Dựng Thương Mại Dịch Vụ Kỹ Thuật H &amp; V</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="n">
-        <v>882964.0</v>
-      </c>
-      <c r="L21" s="13" t="n">
-        <v>70636.0</v>
-      </c>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13" t="n">
-        <v>953600.0</v>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S21" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>C25TBH</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>14/08/2025</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>3502517799</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH VỆ SINH MÔI TRƯỜNG TRUNG DŨNG</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Số 69 đường 16 Tổ 1, ấp 2, Phường Long Hương, TP Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="n">
-        <v>4.888E7</v>
-      </c>
-      <c r="L22" s="13" t="n">
-        <v>3910400.0</v>
-      </c>
-      <c r="M22" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13" t="n">
-        <v>5.27904E7</v>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>C25TTG</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>29/08/2025</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>3702688079</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH CƠ KHÍ TRƯƠNG GIA</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Thửa Đất Số 1073, Tờ Bản Đồ Số 46, Khu Phố Khánh Lộc, Phường Tân Hiệp, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H&amp;V</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="n">
-        <v>2055560.0</v>
-      </c>
-      <c r="L23" s="13" t="n">
-        <v>164440.0</v>
-      </c>
-      <c r="M23" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13" t="n">
-        <v>2220000.0</v>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S23" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/8/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/8/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TBV</t>
+          <t>C25TAD</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>326821</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>15/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0304998358-056</t>
+          <t>0109266456</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH 34 - CÔNG TY CỔ PHẦN THƯƠNG MẠI - DỊCH VỤ PHONG VŨ</t>
+          <t>CÔNG TY CỔ PHẦN GIAO THÔNG SỐ VIỆT NAM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>L11 G2 Đường Nguyễn Thái Học,phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 01 đường Trần Hữu Dực, Phường Từ Liêm, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Công Ty Trách nhiệm hữu hạn đại lý tàu biển vũng tàu</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>360000.0</v>
+        <v>109259.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>0.0</v>
+        <v>8741.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>360000.0</v>
+        <v>118000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,54 +408,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TEM</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>6279310</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>02/08/2025</t>
+          <t>31/08/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>1100119201</t>
+          <t>0109266456</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HIỆP PHÁT</t>
+          <t>CÔNG TY CỔ PHẦN GIAO THÔNG SỐ VIỆT NAM</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>1195 Quốc lộ 1, Khu phố Nhơn Cầu, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
+          <t>Số 01 đường Trần Hữu Dực, Phường Từ Liêm, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Công Ty Trách nhiệm hữu hạn đại lý tàu biển vũng tàu</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>7.61E7</v>
+        <v>283232.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>3805000.0</v>
-      </c>
-      <c r="M8" s="13"/>
+        <v>22659.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>7.9905E7</v>
+        <v>305891.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -489,54 +491,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TDK</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>01/08/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>1100119201</t>
+          <t>3500102326</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HIỆP PHÁT</t>
+          <t>TRUNG TÂM ĐĂNG KIỂM PHƯƠNG TIỆN GIAO THÔNG VẬN TẢI BÀ RỊA VŨNG TÀU</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>1195 Quốc lộ 1, Khu phố Nhơn Cầu, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
+          <t>47B Đường 30/4 - phường Rạch Dừa - TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>8.916E7</v>
+        <v>46000.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>4458000.0</v>
+        <v>3680.0</v>
       </c>
       <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
+      <c r="N9" s="13" t="n">
+        <v>45000.0</v>
+      </c>
       <c r="O9" s="13" t="n">
-        <v>9.3618E7</v>
+        <v>94680.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -570,56 +574,54 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TTH</t>
+          <t>C25THH</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>19/08/2025</t>
+          <t>15/08/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>1100853003</t>
+          <t>3500354108</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGỌC MAI</t>
+          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 46, Nguyễn Văn Cương, Khu phố Nhơn Cầu, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
+          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>8.169E7</v>
+        <v>360000.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>4084500.0</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>36000.0</v>
+      </c>
+      <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>8.57745E7</v>
+        <v>396000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -653,56 +655,54 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TTH</t>
+          <t>C25THH</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>15/08/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>1100853003</t>
+          <t>3500354108</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGỌC MAI</t>
+          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 46, Nguyễn Văn Cương, Khu phố Nhơn Cầu, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
+          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>8.138E7</v>
+        <v>4164444.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>4069000.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>333156.0</v>
+      </c>
+      <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>8.5449E7</v>
+        <v>4497600.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -736,56 +736,54 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TKN</t>
+          <t>C25THH</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>15/08/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>1102099705</t>
+          <t>3500354108</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ GẠO KIM NGÂN</t>
+          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>873 Quốc Lộ 1, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
+          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>8.09E7</v>
+        <v>2338000.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>4045000.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>187040.0</v>
+      </c>
+      <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>8.4945E7</v>
+        <v>2525040.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -819,56 +817,54 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TKN</t>
+          <t>C25TAB</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>93</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>14/08/2025</t>
+          <t>19/08/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>1102099705</t>
+          <t>3501467256</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ GẠO KIM NGÂN</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI KHOA</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>873 Quốc Lộ 1, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
+          <t>Số 20 Ngư Nghiệp, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>8.954E7</v>
+        <v>4296296.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>4477000.0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>343704.0</v>
+      </c>
+      <c r="M13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>9.4017E7</v>
+        <v>4640000.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -902,56 +898,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25TKN</t>
+          <t>C25TTV</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>447</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>23/08/2025</t>
+          <t>18/08/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>1102099705</t>
+          <t>3502528871</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ GẠO KIM NGÂN</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ DU LỊCH THUẦN VIỆT</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>873 Quốc Lộ 1, Phường Khánh Hậu, Tỉnh Tây Ninh, Việt Nam</t>
+          <t>196 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>6.068E7</v>
+        <v>2.4074074E7</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>3034000.0</v>
+        <v>1925926.0</v>
       </c>
       <c r="M14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>6.3714E7</v>
+        <v>2.6E7</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -985,56 +981,56 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25TYA</t>
+          <t>C25TTV</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>27/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>1800348038</t>
+          <t>3502528871</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ADC</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ DU LỊCH THUẦN VIỆT</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>101 Phan Đình Phùng, Phường Ninh Kiều, Thành phố Cần Thơ, Việt Nam</t>
+          <t>196 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>6.55E7</v>
+        <v>2.4074074E7</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>3275000.0</v>
+        <v>1925926.0</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>6.8775E7</v>
+        <v>2.6E7</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>

--- a/Hoadon/HDVao/8/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/8/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TBT</t>
+          <t>C25TBR</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3501772161</t>
+          <t>0316158113</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN BÊ TÔNG VÀ XÂY LẮP HODECO</t>
+          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Thôn 9 Gò Găng, Xã Long Sơn, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1.34440222E8</v>
+        <v>4423022.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1.0755218E7</v>
+        <v>353842.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>1.4519544E8</v>
+        <v>4776864.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -392,6 +392,2320 @@
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25TBR</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>6498</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0316158113</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>4423022.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>353842.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>4776864.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25TMD</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>10035</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3501261826</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH ĐÔNG</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Số 280/3 Trương Công Định, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>1877760.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>150221.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>2027981.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25TMD</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>10036</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3501261826</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH ĐÔNG</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Số 280/3 Trương Công Định, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>572040.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>45763.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>617803.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25TMD</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3501261826</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH ĐÔNG</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Số 280/3 Trương Công Định, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>2449800.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>195984.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>2645784.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25TDL</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>15701</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>29/08/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>4250000.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>340000.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>4590000.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25TDL</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2259</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>4185185.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>334815.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>4520000.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3502397869</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI DỊCH VỤ XUẤT NHẬP KHẨU PHÚ MỸ</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Ấp 4B, Xã Hoà Hội, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>800100.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>40005.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>840105.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>7449</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502420437</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>2407407.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>192593.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>2600000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>01/08/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>4550000.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>227500.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>4777500.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>4480000.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>224000.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>4704000.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>12/08/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>4400000.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>220000.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>4620000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>4550000.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>227500.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>4777500.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>16/08/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>4550000.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>227500.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>4777500.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>4550000.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>227500.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>4777500.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>19/08/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>4620000.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>231000.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>4851000.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>4620000.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>231000.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>4851000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>21/08/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>4555000.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>227750.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>4782750.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>23/08/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>4330000.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>216500.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>4546500.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>4400000.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>220000.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>4620000.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>27/08/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>4400000.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>220000.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>4620000.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>28/08/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>4450000.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>222500.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>4672500.0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>29/08/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>1800000.0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>90000.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>1890000.0</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>05/08/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>4550000.0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>227500.0</v>
+      </c>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>4777500.0</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>4550000.0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>227500.0</v>
+      </c>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>4777500.0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>28/08/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>4666720.0</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>233336.0</v>
+      </c>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>4900056.0</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>29/08/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>4666720.0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>233336.0</v>
+      </c>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>4900056.0</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25TMQ</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3502479416</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>2265000.0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>171000.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>2436000.0</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25TLN</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>18/08/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3602750365</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CỒN - LÊ NGUYỄN</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>A2/189 B, KP 2, Phường Biên Hòa, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>4254640.0</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>340371.0</v>
+      </c>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>4595011.0</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>
